--- a/public/sap-reporting/expansion-150-downloads/EXT-MM25-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM25-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R516a8b84a6744b2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R70d6678e12ee482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R1088b49021d74586"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rceba45c312aa45b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R90dc75a74c2848a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rdb66b55966194ab4"/>
   </x:sheets>
 </x:workbook>
 </file>
